--- a/02.機能設計/端子割り当て.xlsx
+++ b/02.機能設計/端子割り当て.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\01_Software\RaspiPico\DialKeyPad\02.機能設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="11_AD4D066CA252ABDACC10481E5950E8FA73EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BD0CF2E-83F5-40EF-97D5-E0C6BC226A94}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054B025C-C511-4E3B-BD1A-563EDE58C194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8040" yWindow="3000" windowWidth="21060" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7020" yWindow="1305" windowWidth="12570" windowHeight="13590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="端子一覧" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="87">
   <si>
     <t>端子番号</t>
     <rPh sb="0" eb="4">
@@ -225,66 +225,6 @@
   </si>
   <si>
     <t>UART1 RX</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>拡張用ダイアル入力</t>
-    <rPh sb="0" eb="3">
-      <t>カクチョウヨウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダイアル入力</t>
-    <rPh sb="4" eb="6">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LED出力</t>
-    <rPh sb="3" eb="5">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LCD制御 D0</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LCD制御 D1</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LCD制御 D2</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LCD制御 D3</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>E</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -372,16 +312,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>モノクロLCD制御用予約端子</t>
-    <rPh sb="7" eb="10">
-      <t>セイギョヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>ヨヤクタンシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スイッチ入力１</t>
     <rPh sb="4" eb="6">
       <t>ニュウリョク</t>
@@ -413,13 +343,6 @@
     <t>3.3V出力</t>
     <rPh sb="4" eb="6">
       <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>システムバス電源</t>
-    <rPh sb="6" eb="8">
-      <t>デンゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -467,6 +390,135 @@
     </rPh>
     <rPh sb="42" eb="44">
       <t>ソウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コネクタID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>端子</t>
+    <rPh sb="0" eb="2">
+      <t>タンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コネクタ
+端子数</t>
+    <rPh sb="5" eb="8">
+      <t>タンシスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（1-VCC 9-VR 10-GND）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拡張用ダイアル入力(IN)</t>
+    <rPh sb="0" eb="3">
+      <t>カクチョウヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイアル入力(IN)</t>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LED出力(OUT)</t>
+    <rPh sb="3" eb="5">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 D0(OUT)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 D1(OUT)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 D2(OUT)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 D3(OUT)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 RS(OUT)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LCD制御 E(OUT)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スイッチ入力(IN)</t>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムバス電源(5V)</t>
+    <rPh sb="6" eb="8">
+      <t>デンゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -544,7 +596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -567,11 +619,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -580,6 +652,11 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -609,7 +686,7 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>64443</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>164513</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3381,16 +3458,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:F44"/>
+  <dimension ref="B4:J44"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="5" max="5" width="24.375" customWidth="1"/>
     <col min="6" max="6" width="32.625" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:9" ht="37.5">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3404,10 +3483,19 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:9">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -3421,10 +3509,10 @@
         <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:9">
       <c r="B6" s="1">
         <f>B5+1</f>
         <v>2</v>
@@ -3439,10 +3527,10 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:9">
       <c r="B7" s="1">
         <f t="shared" ref="B7:B44" si="0">B6+1</f>
         <v>3</v>
@@ -3460,7 +3548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:9">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3475,10 +3563,10 @@
         <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:9">
       <c r="B9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3493,10 +3581,10 @@
         <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:9">
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3511,10 +3599,10 @@
         <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:9">
       <c r="B11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3529,10 +3617,10 @@
         <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:9">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3550,7 +3638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:9">
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3559,16 +3647,25 @@
         <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:9">
       <c r="B14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3577,16 +3674,25 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:9">
       <c r="B15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3595,16 +3701,25 @@
         <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:9">
       <c r="B16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3613,16 +3728,25 @@
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:9">
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3640,7 +3764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:9">
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3652,13 +3776,22 @@
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:9">
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3670,13 +3803,22 @@
         <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:9">
       <c r="B20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3688,13 +3830,22 @@
         <v>43</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:9">
       <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3706,13 +3857,22 @@
         <v>43</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:9">
       <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3730,7 +3890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:9">
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3740,13 +3900,22 @@
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:9">
       <c r="B24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3756,13 +3925,22 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:9">
       <c r="B25" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3774,13 +3952,22 @@
         <v>40</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:9">
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3792,13 +3979,22 @@
         <v>40</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:9">
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3816,7 +4012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:9">
       <c r="B28" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3828,13 +4024,22 @@
         <v>40</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:9">
       <c r="B29" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3846,13 +4051,22 @@
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:9">
       <c r="B30" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3864,13 +4078,22 @@
         <v>40</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:9">
       <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3882,13 +4105,22 @@
         <v>40</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>62</v>
+      <c r="G31" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31">
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:9">
       <c r="B32" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3906,7 +4138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:10">
       <c r="B33" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3915,16 +4147,26 @@
         <v>35</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33">
+        <v>8</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="J33" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:10">
       <c r="B34" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3936,7 +4178,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:10">
       <c r="B35" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3945,12 +4187,23 @@
         <v>36</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="G35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:10">
       <c r="B36" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3959,12 +4212,23 @@
         <v>37</v>
       </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F36" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:10">
       <c r="B37" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3982,7 +4246,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:10">
       <c r="B38" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3991,12 +4255,23 @@
         <v>38</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
+      </c>
+      <c r="G38" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:10">
       <c r="B39" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -4011,10 +4286,10 @@
         <v>16</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:10">
       <c r="B40" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -4029,10 +4304,10 @@
         <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:10">
       <c r="B41" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -4050,7 +4325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:10">
       <c r="B42" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -4068,7 +4343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:10">
       <c r="B43" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -4080,13 +4355,13 @@
         <v>16</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:10">
       <c r="B44" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -4101,7 +4376,7 @@
         <v>16</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4118,12 +4393,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
